--- a/InputData/endo-learn/BGBSC/BAU Global Battery Storage Cap.xlsx
+++ b/InputData/endo-learn/BGBSC/BAU Global Battery Storage Cap.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-us-analysis\InputData\endo-learn\BGBSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/endo-learn/BGBSC/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5158121-D461-7841-BF32-D18D8284B9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22635" windowHeight="8730"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -57,10 +58,21 @@
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -281,7 +293,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -442,13 +454,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
@@ -464,7 +475,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -477,7 +488,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -485,14 +495,14 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="4"/>
+    <cellStyle name="Normal 10" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
-    <cellStyle name="Table Header 2" xfId="3"/>
+    <cellStyle name="Table Header 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -702,7 +712,7 @@
             <c:numRef>
               <c:f>[1]Sheet1!$G$2:$G$35</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>2375000</c:v>
@@ -1127,7 +1137,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1209,7 +1219,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1217,6 +1226,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1446,7 +1456,7 @@
             <c:numRef>
               <c:f>[1]Sheet1!$G$2:$G$35</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>2375000</c:v>
@@ -1871,7 +1881,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1953,7 +1963,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1961,6 +1970,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5587,7 +5597,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -5713,7 +5729,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -5751,7 +5773,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -5875,7 +5903,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 8"/>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -5905,7 +5939,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="10" name="Chart 9"/>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -5924,7 +5964,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -6529,19 +6569,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="60.86328125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -6549,82 +6589,82 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" s="13">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="12">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B9" s="14" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B9" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B13" s="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="12">
         <v>2020</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B14" s="14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B15" s="14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B15" s="13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>59</v>
       </c>
@@ -6636,19 +6676,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AG8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -6656,7 +6696,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>2020</v>
       </c>
@@ -6679,7 +6719,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6705,7 +6745,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -6738,7 +6778,7 @@
         <v>4345238.0952380942</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6846,339 +6886,339 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AI20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.73046875" customWidth="1"/>
-    <col min="3" max="3" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="5"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
-    <row r="8" spans="1:35" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:35" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7">
         <v>2019</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>2020</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>2021</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>2022</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>2023</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>2024</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="7">
         <v>2025</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="7">
         <v>2026</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="7">
         <v>2027</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="7">
         <v>2028</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="7">
         <v>2029</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="7">
         <v>2030</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="7">
         <v>2031</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="7">
         <v>2032</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="7">
         <v>2033</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="7">
         <v>2034</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="7">
         <v>2035</v>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="7">
         <v>2036</v>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="7">
         <v>2037</v>
       </c>
-      <c r="W9" s="8">
+      <c r="W9" s="7">
         <v>2038</v>
       </c>
-      <c r="X9" s="8">
+      <c r="X9" s="7">
         <v>2039</v>
       </c>
-      <c r="Y9" s="8">
+      <c r="Y9" s="7">
         <v>2040</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="7">
         <v>2041</v>
       </c>
-      <c r="AA9" s="8">
+      <c r="AA9" s="7">
         <v>2042</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AB9" s="7">
         <v>2043</v>
       </c>
-      <c r="AC9" s="8">
+      <c r="AC9" s="7">
         <v>2044</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="7">
         <v>2045</v>
       </c>
-      <c r="AE9" s="8">
+      <c r="AE9" s="7">
         <v>2046</v>
       </c>
-      <c r="AF9" s="8">
+      <c r="AF9" s="7">
         <v>2047</v>
       </c>
-      <c r="AG9" s="8">
+      <c r="AG9" s="7">
         <v>2048</v>
       </c>
-      <c r="AH9" s="8">
+      <c r="AH9" s="7">
         <v>2049</v>
       </c>
-      <c r="AI9" s="8">
+      <c r="AI9" s="7">
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>230</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <f>$D$10+($O$10-$D$10)*(E11/$O$11)</f>
         <v>351.47058823529414</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <f>$D$10+($O$10-$D$10)*(F11/$O$11)</f>
         <v>403.52941176470586</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f t="shared" ref="G10:N10" si="0">$D$10+($O$10-$D$10)*(G11/$O$11)</f>
         <v>498.97058823529409</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <f t="shared" si="0"/>
         <v>603.08823529411757</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
         <v>715.88235294117658</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="15">
         <f t="shared" si="0"/>
         <v>950.14705882352939</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="15">
         <f t="shared" si="0"/>
         <v>1175.7352941176471</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="15">
         <f t="shared" si="0"/>
         <v>1418.6764705882351</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="15">
         <f t="shared" si="0"/>
         <v>1687.6470588235293</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="20">
         <f>2000</f>
         <v>2000</v>
       </c>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>G18/$G$20*10000000</f>
         <v>2375000</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f t="shared" ref="E11:X11" si="1">H18/$G$20*10000000</f>
         <v>1750000</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <f t="shared" si="1"/>
         <v>2500000</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <f t="shared" si="1"/>
         <v>3875000</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <f t="shared" si="1"/>
         <v>5375000</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f t="shared" si="1"/>
         <v>7000000</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <f t="shared" si="1"/>
         <v>8500000</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="8">
         <f t="shared" si="1"/>
         <v>10375000</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <f t="shared" si="1"/>
         <v>13625000</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <f t="shared" si="1"/>
         <v>17125000</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="8">
         <f t="shared" si="1"/>
         <v>21000000</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="8">
         <f t="shared" si="1"/>
         <v>25500000</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="8">
         <f t="shared" si="1"/>
         <v>29250000</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="8">
         <f t="shared" si="1"/>
         <v>33375000</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="8">
         <f t="shared" si="1"/>
         <v>36625000</v>
       </c>
-      <c r="S11" s="9">
+      <c r="S11" s="8">
         <f t="shared" si="1"/>
         <v>39750000</v>
       </c>
-      <c r="T11" s="9">
+      <c r="T11" s="8">
         <f t="shared" si="1"/>
         <v>42625000</v>
       </c>
-      <c r="U11" s="9">
+      <c r="U11" s="8">
         <f t="shared" si="1"/>
         <v>45250000</v>
       </c>
-      <c r="V11" s="9">
+      <c r="V11" s="8">
         <f t="shared" si="1"/>
         <v>47375000</v>
       </c>
-      <c r="W11" s="9">
+      <c r="W11" s="8">
         <f t="shared" si="1"/>
         <v>49375000</v>
       </c>
-      <c r="X11" s="9">
+      <c r="X11" s="8">
         <f t="shared" si="1"/>
         <v>51625000</v>
       </c>
-      <c r="Y11" s="9">
+      <c r="Y11" s="8">
         <f>AB18/$G$20*10000000</f>
         <v>54125000</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="9"/>
-      <c r="AG12" s="9"/>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="9"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="8"/>
+      <c r="AI12" s="8"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="E13" s="12"/>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="E13" s="11"/>
     </row>
-    <row r="17" spans="6:28" x14ac:dyDescent="0.45">
+    <row r="17" spans="6:28" x14ac:dyDescent="0.2">
       <c r="G17">
         <v>2019</v>
       </c>
@@ -7246,7 +7286,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="6:28" x14ac:dyDescent="0.45">
+    <row r="18" spans="6:28" x14ac:dyDescent="0.2">
       <c r="F18" t="s">
         <v>16</v>
       </c>
@@ -7317,7 +7357,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="6:28" x14ac:dyDescent="0.45">
+    <row r="20" spans="6:28" x14ac:dyDescent="0.2">
       <c r="F20" t="s">
         <v>20</v>
       </c>
@@ -7333,910 +7373,908 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
     </row>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <v>104988.75274561244</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="20">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2">
         <v>2019</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <f t="array" ref="G2:G13">TRANSPOSE(Calculations!B12:M12)</f>
         <v>230000</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="18">
         <f t="shared" ref="H2:H33" si="0">min+(max-min)/(1+EXP(-$B$5*(F2-ec_50)))</f>
         <v>278783.70203185978</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="21" t="s">
+      <c r="I2" s="17"/>
+      <c r="J2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
     </row>
-    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>4569491.3134608204</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="20">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3">
         <v>2020</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>351470.58823529416</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="18">
         <f t="shared" si="0"/>
         <v>328267.45651416713</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="19" t="s">
+      <c r="I3" s="17"/>
+      <c r="J3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
     </row>
-    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>2031.231161586554</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="20">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4">
         <v>2021</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>403529.41176470584</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="18">
         <f t="shared" si="0"/>
         <v>390901.62654664449</v>
       </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19" t="s">
+      <c r="I4" s="17"/>
+      <c r="J4" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
     </row>
-    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>0.26214442251490144</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="20">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5">
         <v>2022</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>498970.5882352941</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="18">
         <f t="shared" si="0"/>
         <v>469595.48318729002</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19" t="s">
+      <c r="I5" s="17"/>
+      <c r="J5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
     </row>
-    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="20">
+    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6">
         <v>2023</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>603088.23529411759</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <f t="shared" si="0"/>
         <v>567551.15074796393</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="19" t="s">
+      <c r="I6" s="17"/>
+      <c r="J6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
     </row>
-    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <f>SUMXMY2(G2:G49,H2:H49)</f>
         <v>29259652454.410839</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="20">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7">
         <v>2024</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>715882.35294117662</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <f t="shared" si="0"/>
         <v>688080.8827985992</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19" t="s">
+      <c r="I7" s="17"/>
+      <c r="J7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
     </row>
-    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="20">
+    <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8">
         <v>2025</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>820000</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <f t="shared" si="0"/>
         <v>834293.57521290798</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19" t="s">
+      <c r="I8" s="17"/>
+      <c r="J8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
     </row>
-    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="20">
+    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9">
         <v>2026</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>950147.0588235294</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="18">
         <f t="shared" si="0"/>
         <v>1008633.9439861275</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19" t="s">
+      <c r="I9" s="17"/>
+      <c r="J9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="20">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10">
         <v>2027</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>1175735.294117647</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <f t="shared" si="0"/>
         <v>1212295.4353729906</v>
       </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19" t="s">
+      <c r="I10" s="17"/>
+      <c r="J10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="20">
+    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11">
         <v>2028</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>1418676.4705882352</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="18">
         <f t="shared" si="0"/>
         <v>1444589.739180157</v>
       </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
     </row>
-    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="20">
+    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12">
         <v>2029</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>1687647.0588235292</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <f t="shared" si="0"/>
         <v>1702427.8234259335</v>
       </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="19" t="s">
+      <c r="I12" s="17"/>
+      <c r="J12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="20">
+    <row r="13" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13">
         <v>2030</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>2000000</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="18">
         <f t="shared" si="0"/>
         <v>1980113.8134141492</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="19" t="s">
+      <c r="I13" s="17"/>
+      <c r="J13" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
     </row>
-    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="20">
+    <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14">
         <v>2031</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <f t="array" ref="G14:G23">TRANSPOSE(Calculations!N13:W13)</f>
         <v>2294117.6470588231</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="18">
         <f t="shared" si="0"/>
         <v>2269626.0524723819</v>
       </c>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
     </row>
-    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="20">
+    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15">
         <v>2032</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>2617647.0588235296</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <f t="shared" si="0"/>
         <v>2561433.0745960292</v>
       </c>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="20">
+    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16">
         <v>2033</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>2872549.0196078434</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="18">
         <f t="shared" si="0"/>
         <v>2845699.7623751801</v>
       </c>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
     </row>
-    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="20">
+    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17">
         <v>2034</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>3117647.0588235296</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="18">
         <f t="shared" si="0"/>
         <v>3113575.7210382498</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
     </row>
-    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="20">
+    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18">
         <v>2035</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>3343137.254901961</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="18">
         <f t="shared" si="0"/>
         <v>3358221.5158605184</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
     </row>
-    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="20">
+    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19">
         <v>2036</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>3549019.6078431369</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="18">
         <f t="shared" si="0"/>
         <v>3575342.1035233433</v>
       </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
     </row>
-    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="20">
+    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20">
         <v>2037</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>3715686.2745098039</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="18">
         <f t="shared" si="0"/>
         <v>3763189.6578150792</v>
       </c>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
     </row>
-    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="20">
+    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21">
         <v>2038</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>3872549.0196078434</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="18">
         <f t="shared" si="0"/>
         <v>3922163.6311920611</v>
       </c>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
     </row>
-    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="20">
+    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22">
         <v>2039</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>4049019.6078431369</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="18">
         <f t="shared" si="0"/>
         <v>4054208.6165724192</v>
       </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="18"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
     </row>
-    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="20">
+    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23">
         <v>2040</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>4245098.0392156867</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <f t="shared" si="0"/>
         <v>4162192.4631264298</v>
       </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
     </row>
-    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="23">
+    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="21">
         <v>2041</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19">
+      <c r="G24" s="17"/>
+      <c r="H24" s="18">
         <f t="shared" si="0"/>
         <v>4249381.218936245</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-      <c r="P24" s="18"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
     </row>
-    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="23">
+    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="21">
         <v>2042</v>
       </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19">
+      <c r="G25" s="17"/>
+      <c r="H25" s="18">
         <f t="shared" si="0"/>
         <v>4319057.8987108367</v>
       </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
     </row>
-    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="23">
+    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="21">
         <v>2043</v>
       </c>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19">
+      <c r="G26" s="17"/>
+      <c r="H26" s="18">
         <f t="shared" si="0"/>
         <v>4374282.7762160646</v>
       </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
     </row>
-    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="23">
+    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="21">
         <v>2044</v>
       </c>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19">
+      <c r="G27" s="17"/>
+      <c r="H27" s="18">
         <f t="shared" si="0"/>
         <v>4417768.075591377</v>
       </c>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
     </row>
-    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="23">
+    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="21">
         <v>2045</v>
       </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19">
+      <c r="G28" s="17"/>
+      <c r="H28" s="18">
         <f t="shared" si="0"/>
         <v>4451833.4089139272</v>
       </c>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
     </row>
-    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="23">
+    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="21">
         <v>2046</v>
       </c>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19">
+      <c r="G29" s="17"/>
+      <c r="H29" s="18">
         <f t="shared" si="0"/>
         <v>4478411.8204253027</v>
       </c>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
     </row>
-    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="23">
+    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="21">
         <v>2047</v>
       </c>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19">
+      <c r="G30" s="17"/>
+      <c r="H30" s="18">
         <f t="shared" si="0"/>
         <v>4499083.5324107874</v>
       </c>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
     </row>
-    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="23">
+    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="21">
         <v>2048</v>
       </c>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19">
+      <c r="G31" s="17"/>
+      <c r="H31" s="18">
         <f t="shared" si="0"/>
         <v>4515121.8487209175</v>
       </c>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
     </row>
-    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="23">
+    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="21">
         <v>2049</v>
       </c>
-      <c r="G32" s="18"/>
-      <c r="H32" s="19">
+      <c r="G32" s="17"/>
+      <c r="H32" s="18">
         <f t="shared" si="0"/>
         <v>4527541.6461870577</v>
       </c>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
     </row>
-    <row r="33" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="23">
+    <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="21">
         <v>2050</v>
       </c>
-      <c r="G33" s="18"/>
-      <c r="H33" s="19">
+      <c r="G33" s="17"/>
+      <c r="H33" s="18">
         <f t="shared" si="0"/>
         <v>4537145.1567553291</v>
       </c>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
     </row>
-    <row r="34" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
+    <row r="34" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
     </row>
-    <row r="35" spans="1:16" ht="15" x14ac:dyDescent="0.45">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
+    <row r="35" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8245,32 +8283,32 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AH18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.86328125" customWidth="1"/>
-    <col min="2" max="2" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2019</v>
       </c>
@@ -8368,11 +8406,11 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <f>'Grid Battery Storage'!B6</f>
         <v>23809.523809523806</v>
       </c>
@@ -8501,17 +8539,17 @@
         <v>4345238.0952380896</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2019</v>
       </c>
@@ -8609,7 +8647,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -8662,7 +8700,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -8707,7 +8745,7 @@
         <v>4245098.0392156867</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -8752,7 +8790,7 @@
         <v>4537145.1567553291</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>2018</v>
       </c>
@@ -8853,7 +8891,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -8986,11 +9024,11 @@
         <v>88901245.029926673</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>2500</v>
       </c>
     </row>
@@ -9002,20 +9040,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BA2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.73046875" customWidth="1"/>
-    <col min="2" max="2" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="13" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="35" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="2" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="35" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>2019</v>
       </c>
@@ -9112,138 +9149,278 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1">
+        <v>2051</v>
+      </c>
+      <c r="AI1">
+        <v>2052</v>
+      </c>
+      <c r="AJ1">
+        <v>2053</v>
+      </c>
+      <c r="AK1">
+        <v>2054</v>
+      </c>
+      <c r="AL1">
+        <v>2055</v>
+      </c>
+      <c r="AM1">
+        <v>2056</v>
+      </c>
+      <c r="AN1">
+        <v>2057</v>
+      </c>
+      <c r="AO1">
+        <v>2058</v>
+      </c>
+      <c r="AP1">
+        <v>2059</v>
+      </c>
+      <c r="AQ1">
+        <v>2060</v>
+      </c>
+      <c r="AR1">
+        <v>2061</v>
+      </c>
+      <c r="AS1">
+        <v>2062</v>
+      </c>
+      <c r="AT1">
+        <v>2063</v>
+      </c>
+      <c r="AU1">
+        <v>2064</v>
+      </c>
+      <c r="AV1">
+        <v>2065</v>
+      </c>
+      <c r="AW1">
+        <v>2066</v>
+      </c>
+      <c r="AX1">
+        <v>2067</v>
+      </c>
+      <c r="AY1">
+        <v>2068</v>
+      </c>
+      <c r="AZ1">
+        <v>2069</v>
+      </c>
+      <c r="BA1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <f>Calculations!B6+Calculations!C17</f>
         <v>253809.52380952382</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <f>Calculations!C6+Calculations!D17</f>
         <v>605280.1120448166</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <f>Calculations!D6+Calculations!E17</f>
         <v>1035000</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <f>Calculations!E6+Calculations!F17</f>
         <v>1560161.0644257716</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <f>Calculations!F6+Calculations!G17</f>
         <v>2189439.7759103668</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <f>Calculations!G6+Calculations!H17</f>
         <v>2931512.6050420208</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <f>Calculations!H6+Calculations!I17</f>
         <v>3777703.0812324909</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <f>Calculations!I6+Calculations!J17</f>
         <v>4811183.4733893415</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <f>Calculations!J6+Calculations!K17</f>
         <v>6070252.100840332</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <f>Calculations!K6+Calculations!L17</f>
         <v>7572261.9047619104</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="10">
         <f>Calculations!L6+Calculations!M17</f>
         <v>9343242.2969187535</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <f>Calculations!M6+Calculations!N17</f>
         <v>11426575.630252097</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="10">
         <f>Calculations!N6+Calculations!O17</f>
         <v>13834978.99159665</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="10">
         <f>Calculations!O6+Calculations!P17</f>
         <v>16566911.764705881</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="10">
         <f>Calculations!P6+Calculations!Q17</f>
         <v>19553746.498599455</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="10">
         <f>Calculations!Q6+Calculations!R17</f>
         <v>22785679.271708686</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="10">
         <f>Calculations!R6+Calculations!S17</f>
         <v>26243102.240896348</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="10">
         <f>Calculations!S6+Calculations!T17</f>
         <v>29968312.324929934</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="10">
         <f>Calculations!T6+Calculations!U17</f>
         <v>33860189.075630248</v>
       </c>
-      <c r="U2" s="11">
+      <c r="U2" s="10">
         <f>Calculations!U6+Calculations!V17</f>
         <v>37908928.571428537</v>
       </c>
-      <c r="V2" s="11">
+      <c r="V2" s="10">
         <f>Calculations!V6+Calculations!W17</f>
         <v>42134138.655462183</v>
       </c>
-      <c r="W2" s="11">
+      <c r="W2" s="10">
         <f>Calculations!W6+Calculations!X17</f>
         <v>46555427.170868315</v>
       </c>
-      <c r="X2" s="11">
+      <c r="X2" s="10">
         <f>Calculations!X6+Calculations!Y17</f>
         <v>51042903.62789984</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="Y2" s="10">
         <f>Calculations!Y6+Calculations!Z17</f>
         <v>55600056.764705963</v>
       </c>
-      <c r="Z2" s="11">
+      <c r="Z2" s="10">
         <f>Calculations!Z6+Calculations!AA17</f>
         <v>60212434.779017255</v>
       </c>
-      <c r="AA2" s="11">
+      <c r="AA2" s="10">
         <f>Calculations!AA6+Calculations!AB17</f>
         <v>64868298.092703857</v>
       </c>
-      <c r="AB2" s="11">
+      <c r="AB2" s="10">
         <f>Calculations!AB6+Calculations!AC17</f>
         <v>69558226.739713013</v>
       </c>
-      <c r="AC2" s="11">
+      <c r="AC2" s="10">
         <f>Calculations!AC6+Calculations!AD17</f>
         <v>74262829.036328763</v>
       </c>
-      <c r="AD2" s="11">
+      <c r="AD2" s="10">
         <f>Calculations!AD6+Calculations!AE17</f>
         <v>78988103.044930056</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="AE2" s="10">
         <f>Calculations!AE6+Calculations!AF17</f>
         <v>83729415.369841427</v>
       </c>
-      <c r="AF2" s="11">
+      <c r="AF2" s="10">
         <f>Calculations!AF6+Calculations!AG17</f>
         <v>88483147.492218927</v>
       </c>
-      <c r="AG2" s="11">
+      <c r="AG2" s="10">
         <f>Calculations!AG6+Calculations!AH17</f>
         <v>93246483.125164762</v>
+      </c>
+      <c r="AH2">
+        <f>_xlfn.FORECAST.LINEAR(AH1,$B$2:$AG$2,$B$1:$AG$1)</f>
+        <v>84695504.782649994</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" ref="AI2:BA2" si="0">_xlfn.FORECAST.LINEAR(AI1,$B$2:$AG$2,$B$1:$AG$1)</f>
+        <v>87819134.363781929</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>90942763.944914818</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>94066393.526046753</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>97190023.107178688</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>100313652.68831158</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>103437282.26944351</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>106560911.85057545</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>109684541.43170738</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>112808171.01284027</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>115931800.59397221</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>119055430.17510414</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>122179059.75623703</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>125302689.33736897</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>128426318.9185009</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>131549948.49963379</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>134673578.08076572</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>137797207.66189766</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>140920837.24303055</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>144044466.82416248</v>
       </c>
     </row>
   </sheetData>
